--- a/spark-cv/data/cv_entries.xlsx
+++ b/spark-cv/data/cv_entries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{255DD409-DE3F-4154-B8FF-D21BFFE4C49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5C0356-DC8A-4FC1-9538-7A39B54F9729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
   <si>
     <t>type</t>
   </si>
@@ -279,15 +279,6 @@
     <t>Graduate Research Assistant</t>
   </si>
   <si>
-    <t>Colorado State University, Fort Collins, CO, United States</t>
-  </si>
-  <si>
-    <t>Texas A&amp;M AgriLife Research, Temple, TX, United States</t>
-  </si>
-  <si>
-    <t>[Ryan Bailey’s Lab](https://jtcox94.wixsite.com/rtbailey) in Dept. of Civil Engineering, Colorado State University, Fort Collins, CO, United States</t>
-  </si>
-  <si>
     <t>IT &amp; Computer Instructor</t>
   </si>
   <si>
@@ -306,13 +297,40 @@
     <t>2014</t>
   </si>
   <si>
-    <t>HWASHIN Engineering &amp; Bio Technology Co., Ltd., Incheon, South Korea</t>
-  </si>
-  <si>
-    <t>University of Suwon, Suwon, South Korea</t>
-  </si>
-  <si>
-    <t>Intercultural Institute of California (IIC), San Francisco, CA, United States</t>
+    <t>Colorado State University</t>
+  </si>
+  <si>
+    <t>Fort Collins, CO, United States</t>
+  </si>
+  <si>
+    <t>loc</t>
+  </si>
+  <si>
+    <t>University of Suwon</t>
+  </si>
+  <si>
+    <t>Suwon, South Korea</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M AgriLife Research</t>
+  </si>
+  <si>
+    <t>Temple, TX, United States</t>
+  </si>
+  <si>
+    <t>[Ryan Bailey’s Lab](https://jtcox94.wixsite.com/rtbailey) in Dept. of Civil Engineering, Colorado State University</t>
+  </si>
+  <si>
+    <t>Intercultural Institute of California (IIC)</t>
+  </si>
+  <si>
+    <t>San Francisco, CA, United States</t>
+  </si>
+  <si>
+    <t>Incheon, South Korea</t>
+  </si>
+  <si>
+    <t>HWASHIN Engineering &amp; Bio Technology Co., Ltd.</t>
   </si>
 </sst>
 </file>
@@ -712,19 +730,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D849796-8D2F-2144-8637-FA01837A8DE5}">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="49.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.375" customWidth="1"/>
-    <col min="6" max="6" width="35.375" customWidth="1"/>
-    <col min="7" max="7" width="27.625" customWidth="1"/>
+    <col min="5" max="6" width="49.375" customWidth="1"/>
+    <col min="7" max="7" width="35.375" customWidth="1"/>
+    <col min="8" max="8" width="27.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -741,22 +759,25 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>76</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -770,24 +791,27 @@
         <v>68</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -801,13 +825,16 @@
         <v>71</v>
       </c>
       <c r="E4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" t="s">
         <v>91</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -815,7 +842,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -829,13 +856,16 @@
         <v>72</v>
       </c>
       <c r="E6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F6" t="s">
         <v>91</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>11</v>
       </c>
@@ -847,11 +877,14 @@
         <v>75</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="F7" s="12"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="12"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
@@ -865,12 +898,15 @@
         <v>79</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="J8" s="5"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="K8" s="5"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
@@ -884,50 +920,59 @@
         <v>80</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="1"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="J10" s="5"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="1"/>
+      <c r="K10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="J11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="1"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -942,7 +987,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -957,7 +1002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -972,7 +1017,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -987,7 +1032,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1002,7 +1047,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1019,7 +1064,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1035,11 +1080,11 @@
       <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1056,7 +1101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1069,8 +1114,9 @@
       <c r="E20" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>30</v>
       </c>
@@ -1083,8 +1129,9 @@
       <c r="E21" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1098,7 +1145,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>46</v>
       </c>
@@ -1106,7 +1153,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -1114,7 +1161,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>46</v>
       </c>
@@ -1122,7 +1169,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>46</v>
       </c>
@@ -1130,7 +1177,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -1138,7 +1185,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>46</v>
       </c>
@@ -1146,7 +1193,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -1154,7 +1201,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -1162,7 +1209,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -1170,7 +1217,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -1178,7 +1225,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>47</v>
       </c>
@@ -1189,7 +1236,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>47</v>
       </c>
@@ -1200,7 +1247,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>47</v>
       </c>
@@ -1210,11 +1257,11 @@
       <c r="D35" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>49</v>
       </c>
@@ -1222,7 +1269,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -1230,18 +1277,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>49</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>55</v>
       </c>
@@ -1257,13 +1304,13 @@
       <c r="E39" t="s">
         <v>10</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>57</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G3" r:id="rId1" xr:uid="{C848EE18-9B31-4FDE-AB85-25683CAB6CDB}"/>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{C848EE18-9B31-4FDE-AB85-25683CAB6CDB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/spark-cv/data/cv_entries.xlsx
+++ b/spark-cv/data/cv_entries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5C0356-DC8A-4FC1-9538-7A39B54F9729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DFBD71-432D-4A37-8556-83CD386B916A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
+    <workbookView xWindow="19665" yWindow="3810" windowWidth="21600" windowHeight="11505" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="110">
   <si>
     <t>type</t>
   </si>
@@ -129,21 +129,6 @@
     <t>workshop-delivered</t>
   </si>
   <si>
-    <t xml:space="preserve">Developing transparent and reproducible research with R </t>
-  </si>
-  <si>
-    <t>Training provided at the Annual meeting of the American Educational Research Association, Toronto, ON</t>
-  </si>
-  <si>
-    <t>Winter, 2017</t>
-  </si>
-  <si>
-    <t>A taste of R: Mini-course on R (4 sessions, two hours each)</t>
-  </si>
-  <si>
-    <t>Training provided for University of Oregon faculty in the College of Education</t>
-  </si>
-  <si>
     <t>Educational Researcher</t>
   </si>
   <si>
@@ -180,27 +165,15 @@
     <t>award</t>
   </si>
   <si>
-    <t>Outstanding reviewer: *Educational Researcher*</t>
-  </si>
-  <si>
     <t>affiliation</t>
   </si>
   <si>
-    <t>American Educational Research Association</t>
-  </si>
-  <si>
-    <t>National Council of Measurement in Education</t>
-  </si>
-  <si>
     <t>https://hpcf.uoregon.edu</t>
   </si>
   <si>
     <t>current</t>
   </si>
   <si>
-    <t>Terminal project of distinction</t>
-  </si>
-  <si>
     <t>doc-committee</t>
   </si>
   <si>
@@ -210,18 +183,9 @@
     <t>Maximizing pilot phase measures to inform quality improvement: Using a sequential mixed methods design with interrupted time series to examine feasibility, uptake, and drivers of an evidence based practice in part c/early intervention systems</t>
   </si>
   <si>
-    <t>April, 2019</t>
-  </si>
-  <si>
     <t>Core Member (two-year appointment): Social Systems Data Science Network</t>
   </si>
   <si>
-    <t>Data Visualization Society</t>
-  </si>
-  <si>
-    <t>https://www.datavisualizationsociety.com</t>
-  </si>
-  <si>
     <t>2020</t>
   </si>
   <si>
@@ -234,12 +198,6 @@
     <t>COE Quantitative Curriculum Review Committee Member</t>
   </si>
   <si>
-    <t>Awarded for outstanding Master's degree Terminal Project, University of Oregon College of Education</t>
-  </si>
-  <si>
-    <t>*Data Science Fellow*: College of Education, University of Oregon</t>
-  </si>
-  <si>
     <t>Ph.D., in Civil Engineering, Groundwater Engineering</t>
   </si>
   <si>
@@ -331,12 +289,91 @@
   </si>
   <si>
     <t>HWASHIN Engineering &amp; Bio Technology Co., Ltd.</t>
+  </si>
+  <si>
+    <t>Introduction to SWAT-MODFLOW / Model Optimization with PEST</t>
+  </si>
+  <si>
+    <t>Aarhus University</t>
+  </si>
+  <si>
+    <t>participants</t>
+  </si>
+  <si>
+    <t>Aarhus, Denmark</t>
+  </si>
+  <si>
+    <t>2018 International SWAT Conference</t>
+  </si>
+  <si>
+    <t>9th International Congress on Environmental Modelling &amp; Software</t>
+  </si>
+  <si>
+    <t>Vienna, Austria</t>
+  </si>
+  <si>
+    <t>2019 International SWAT Conference</t>
+  </si>
+  <si>
+    <t>SWAT-MODFLOW / QSWATMOD with Dr. Ryan Bailey</t>
+  </si>
+  <si>
+    <t>Brussels, Belgium</t>
+  </si>
+  <si>
+    <t>Introduction to QSWATMOD</t>
+  </si>
+  <si>
+    <t>Jul. 15-16, 2019</t>
+  </si>
+  <si>
+    <t>Sep. 17-18, 2018</t>
+  </si>
+  <si>
+    <t>Jun. 24-28, 2018</t>
+  </si>
+  <si>
+    <t>Nov. 16, 2017</t>
+  </si>
+  <si>
+    <t>Whitney Borland Scholarship</t>
+  </si>
+  <si>
+    <t>Hwashin E&amp;B Affiliated Research Institute Foundation Research Award</t>
+  </si>
+  <si>
+    <t>Hwashin E&amp;B</t>
+  </si>
+  <si>
+    <t>invited-talks</t>
+  </si>
+  <si>
+    <t>Aug. 11, 2016</t>
+  </si>
+  <si>
+    <t>Introduction to the SWAT-MODFLOW model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulsan National Institute of Science and Technology (UNIST) </t>
+  </si>
+  <si>
+    <t>Ulsan, South Korea</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> American Water Resources Association</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> American Geophysical Union</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -393,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -415,6 +452,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -730,19 +770,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D849796-8D2F-2144-8637-FA01837A8DE5}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="49.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="49.375" customWidth="1"/>
-    <col min="7" max="7" width="35.375" customWidth="1"/>
-    <col min="8" max="8" width="27.625" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35.375" customWidth="1"/>
+    <col min="9" max="9" width="27.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -759,25 +800,28 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="G1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" t="s">
-        <v>76</v>
-      </c>
       <c r="K1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="L1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -788,30 +832,30 @@
         <v>2018</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="F2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -822,27 +866,27 @@
         <v>2006</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -853,38 +897,38 @@
         <v>2007</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E6" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="12" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="H7" s="12"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>11</v>
       </c>
@@ -892,21 +936,22 @@
         <v>21</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="F8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="G8" s="1"/>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G8" s="7"/>
+      <c r="H8" s="1"/>
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>11</v>
       </c>
@@ -917,77 +962,80 @@
         <v>21</v>
       </c>
       <c r="D9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>94</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G9" s="1"/>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="G9" s="7"/>
+      <c r="H9" s="1"/>
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G10" s="7"/>
+      <c r="H10" s="1"/>
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D11" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>98</v>
-      </c>
       <c r="F11" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="G11" s="7"/>
+      <c r="H11" s="1"/>
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1002,7 +1050,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1017,7 +1065,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1032,7 +1080,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1047,7 +1095,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1055,16 +1103,16 @@
         <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1072,7 +1120,7 @@
         <v>2018</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>26</v>
@@ -1080,11 +1128,11 @@
       <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="H18" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1092,16 +1140,16 @@
         <v>2019</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1115,202 +1163,278 @@
         <v>29</v>
       </c>
       <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C21" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" s="13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
       <c r="C22" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
+        <v>86</v>
+      </c>
+      <c r="F24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" t="s">
+        <v>107</v>
+      </c>
+      <c r="G25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="3" t="s">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E22" t="s">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="1" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="1" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="1" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33">
-        <v>2021</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34">
-        <v>2017</v>
+        <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35">
-        <v>2009</v>
+        <v>41</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G35" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="C36">
+        <v>2017</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>50</v>
+        <v>100</v>
+      </c>
+      <c r="E36" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" s="14">
+        <v>5000</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="C37">
+        <v>2016</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="E37" t="s">
+        <v>73</v>
+      </c>
+      <c r="H37" s="15">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="C38">
+        <v>2014</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H38" t="s">
-        <v>61</v>
+        <v>101</v>
+      </c>
+      <c r="E38" t="s">
+        <v>102</v>
+      </c>
+      <c r="H38" s="14">
+        <v>24000</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39">
+        <v>43</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41">
         <v>2018</v>
       </c>
-      <c r="C39">
+      <c r="C41">
         <v>2019</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E39" t="s">
+      <c r="D41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" t="s">
         <v>10</v>
       </c>
-      <c r="G39" t="s">
-        <v>57</v>
+      <c r="H41" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{C848EE18-9B31-4FDE-AB85-25683CAB6CDB}"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{C848EE18-9B31-4FDE-AB85-25683CAB6CDB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/spark-cv/data/cv_entries.xlsx
+++ b/spark-cv/data/cv_entries.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29DFBD71-432D-4A37-8556-83CD386B916A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B59861-C0C6-4ED5-84A8-EE2F87442363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19665" yWindow="3810" windowWidth="21600" windowHeight="11505" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
@@ -330,9 +330,6 @@
     <t>Sep. 17-18, 2018</t>
   </si>
   <si>
-    <t>Jun. 24-28, 2018</t>
-  </si>
-  <si>
     <t>Nov. 16, 2017</t>
   </si>
   <si>
@@ -364,6 +361,9 @@
   </si>
   <si>
     <t xml:space="preserve"> American Geophysical Union</t>
+  </si>
+  <si>
+    <t>Jun. 24, 2018</t>
   </si>
 </sst>
 </file>
@@ -372,7 +372,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -454,7 +454,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1210,7 +1210,7 @@
         <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>95</v>
@@ -1230,7 +1230,7 @@
         <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>85</v>
@@ -1247,19 +1247,19 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" t="s">
         <v>103</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" t="s">
         <v>105</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>106</v>
-      </c>
-      <c r="F25" t="s">
-        <v>107</v>
       </c>
       <c r="G25">
         <v>17</v>
@@ -1353,7 +1353,7 @@
         <v>2017</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E36" t="s">
         <v>73</v>
@@ -1370,7 +1370,7 @@
         <v>2016</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E37" t="s">
         <v>73</v>
@@ -1387,10 +1387,10 @@
         <v>2014</v>
       </c>
       <c r="D38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E38" t="s">
         <v>101</v>
-      </c>
-      <c r="E38" t="s">
-        <v>102</v>
       </c>
       <c r="H38" s="14">
         <v>24000</v>
@@ -1401,7 +1401,7 @@
         <v>43</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -1409,7 +1409,7 @@
         <v>43</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">

--- a/spark-cv/data/cv_entries.xlsx
+++ b/spark-cv/data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B59861-C0C6-4ED5-84A8-EE2F87442363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A386A4-D965-44BF-BC22-5401F47F88AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19665" yWindow="3810" windowWidth="21600" windowHeight="11505" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="115">
   <si>
     <t>type</t>
   </si>
@@ -364,6 +364,21 @@
   </si>
   <si>
     <t>Jun. 24, 2018</t>
+  </si>
+  <si>
+    <t>Virtual</t>
+  </si>
+  <si>
+    <t>ArcAPEX for Agricultural Watershed Modeling Workshop | APEX-MODFLOW (3rd Day)</t>
+  </si>
+  <si>
+    <t>Mar. 16-18, 2022</t>
+  </si>
+  <si>
+    <t>Salinity Modeling Workshop (3 hours-session)</t>
+  </si>
+  <si>
+    <t>Jan. 26, 2022</t>
   </si>
 </sst>
 </file>
@@ -403,7 +418,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,6 +428,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,7 +451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -452,9 +473,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -770,13 +796,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D849796-8D2F-2144-8637-FA01837A8DE5}">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="49.375" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.375" customWidth="1"/>
@@ -1165,128 +1191,146 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+    <row r="21" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="17"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C22" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G22" s="15">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" s="15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D24" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E24" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F24" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G24" s="15">
         <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" t="s">
-        <v>97</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" t="s">
-        <v>88</v>
-      </c>
-      <c r="G24">
-        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E25" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25" t="s">
-        <v>106</v>
-      </c>
-      <c r="G25">
-        <v>17</v>
+        <v>93</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="C27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" t="s">
+        <v>88</v>
+      </c>
+      <c r="G27">
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>33</v>
+        <v>102</v>
+      </c>
+      <c r="C28" t="s">
+        <v>103</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" t="s">
+        <v>106</v>
+      </c>
+      <c r="G28">
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1294,7 +1338,7 @@
         <v>41</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1302,7 +1346,7 @@
         <v>41</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1310,7 +1354,7 @@
         <v>41</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1318,7 +1362,7 @@
         <v>41</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1326,7 +1370,7 @@
         <v>41</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1334,7 +1378,7 @@
         <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1342,93 +1386,117 @@
         <v>41</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36">
-        <v>2017</v>
+        <v>41</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E36" t="s">
-        <v>73</v>
-      </c>
-      <c r="H36" s="14">
-        <v>5000</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37">
-        <v>2016</v>
+        <v>41</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E37" t="s">
-        <v>73</v>
-      </c>
-      <c r="H37" s="15">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38">
-        <v>2014</v>
+        <v>41</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E38" t="s">
-        <v>101</v>
-      </c>
-      <c r="H38" s="14">
-        <v>24000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="C39">
+        <v>2017</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>108</v>
+        <v>99</v>
+      </c>
+      <c r="E39" t="s">
+        <v>73</v>
+      </c>
+      <c r="H39" s="13">
+        <v>5000</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40">
+        <v>2016</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E40" t="s">
+        <v>73</v>
+      </c>
+      <c r="H40" s="14">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41">
+        <v>2014</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" t="s">
+        <v>101</v>
+      </c>
+      <c r="H41" s="13">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>43</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D42" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>46</v>
       </c>
-      <c r="B41">
+      <c r="B44">
         <v>2018</v>
       </c>
-      <c r="C41">
+      <c r="C44">
         <v>2019</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E44" t="s">
         <v>10</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H44" t="s">
         <v>48</v>
       </c>
     </row>

--- a/spark-cv/data/cv_entries.xlsx
+++ b/spark-cv/data/cv_entries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A386A4-D965-44BF-BC22-5401F47F88AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44448288-81F5-4994-BFC1-850C0D241297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21390" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
+    <workbookView xWindow="3165" yWindow="2295" windowWidth="25050" windowHeight="15555" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="1" r:id="rId1"/>
@@ -870,7 +870,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -904,7 +904,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -917,10 +917,10 @@
         <v>1</v>
       </c>
       <c r="B6">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="C6">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>58</v>
@@ -1106,7 +1106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>

--- a/spark-cv/data/cv_entries.xlsx
+++ b/spark-cv/data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44448288-81F5-4994-BFC1-850C0D241297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9FE36C-3575-4397-B388-53EDA95DC00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3165" yWindow="2295" windowWidth="25050" windowHeight="15555" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
+    <workbookView xWindow="3465" yWindow="3465" windowWidth="38700" windowHeight="15555" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="137">
   <si>
     <t>type</t>
   </si>
@@ -379,6 +379,72 @@
   </si>
   <si>
     <t>Jan. 26, 2022</t>
+  </si>
+  <si>
+    <t>Apr. 28, 2022</t>
+  </si>
+  <si>
+    <t>Fundammentals of Hydrogeology and Model Applications</t>
+  </si>
+  <si>
+    <t>Dankook University</t>
+  </si>
+  <si>
+    <t>Cheonan, South Korea</t>
+  </si>
+  <si>
+    <t>May 4,2022</t>
+  </si>
+  <si>
+    <t>National Academy of Agricultural Sciences</t>
+  </si>
+  <si>
+    <t>Wanju-gun, South Korea</t>
+  </si>
+  <si>
+    <t>Overview of SWAT / SWAT+</t>
+  </si>
+  <si>
+    <t>Assessment of spatio-temporal variation of water resource and fluxes using integrated models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jun. 23, 2022 </t>
+  </si>
+  <si>
+    <t>2022 UST Global Mentoring Conference</t>
+  </si>
+  <si>
+    <t>Blackland Research and Extension Center, Temple, TX</t>
+  </si>
+  <si>
+    <t>May 6,2022</t>
+  </si>
+  <si>
+    <t>SWAT-MODFLOW / QSWATMOD</t>
+  </si>
+  <si>
+    <t>Ulsan National Institute of Science and Technology (UNIST)</t>
+  </si>
+  <si>
+    <t>Jul. 27-29, 2022</t>
+  </si>
+  <si>
+    <t>SWAT-MODFLOW Workshop</t>
+  </si>
+  <si>
+    <t>Korea Institute of Civil Engineering and Building Technology</t>
+  </si>
+  <si>
+    <t>Goyang, South Korea</t>
+  </si>
+  <si>
+    <t>editor</t>
+  </si>
+  <si>
+    <t>Guest editor</t>
+  </si>
+  <si>
+    <t>[Special Issue "Impact of Climate Change on Watershed Hydrology: Latest Advances and Prospects"](https://www.mdpi.com/journal/sustainability/special_issues/19FXHY6N6X), Sustainability</t>
   </si>
 </sst>
 </file>
@@ -418,7 +484,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,6 +503,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -451,7 +523,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -481,6 +553,15 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -796,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D849796-8D2F-2144-8637-FA01837A8DE5}">
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L55"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -1199,304 +1280,449 @@
     </row>
     <row r="22" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="7">
+        <v>2022</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="I22" s="25"/>
+    </row>
+    <row r="23" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D23" s="9"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+    </row>
+    <row r="24" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D24" s="9"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+    </row>
+    <row r="25" spans="1:9" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="23"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+    </row>
+    <row r="26" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C26" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="G26" s="15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="G27" s="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D28" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15" t="s">
+      <c r="E28" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G28" s="15">
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
+    <row r="29" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D29" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15" t="s">
+      <c r="E29" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F29" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G29" s="15">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+    <row r="30" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C30" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D30" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E30" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F30" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G30" s="15">
         <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="G25" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G26" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E27" t="s">
-        <v>86</v>
-      </c>
-      <c r="F27" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" t="s">
-        <v>103</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" t="s">
-        <v>105</v>
-      </c>
-      <c r="F28" t="s">
-        <v>106</v>
-      </c>
-      <c r="G28">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="3">
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G32" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>98</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E33" t="s">
+        <v>86</v>
+      </c>
+      <c r="F33" t="s">
+        <v>88</v>
+      </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D34" s="20"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" t="s">
+        <v>110</v>
+      </c>
+      <c r="G35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>102</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E36" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" t="s">
+        <v>121</v>
+      </c>
+      <c r="G36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>102</v>
+      </c>
+      <c r="C37" t="s">
+        <v>115</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E37" t="s">
+        <v>117</v>
+      </c>
+      <c r="F37" t="s">
+        <v>118</v>
+      </c>
+      <c r="G37">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" t="s">
+        <v>105</v>
+      </c>
+      <c r="F38" t="s">
+        <v>106</v>
+      </c>
+      <c r="G38">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D39" s="3"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>41</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D40" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>41</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>41</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D47" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>41</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D48" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>42</v>
       </c>
-      <c r="C39">
+      <c r="C50">
         <v>2017</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E50" t="s">
         <v>73</v>
       </c>
-      <c r="H39" s="13">
+      <c r="H50" s="13">
         <v>5000</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>42</v>
       </c>
-      <c r="C40">
+      <c r="C51">
         <v>2016</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E51" t="s">
         <v>73</v>
       </c>
-      <c r="H40" s="14">
+      <c r="H51" s="14">
         <v>5000</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>42</v>
       </c>
-      <c r="C41">
+      <c r="C52">
         <v>2014</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D52" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E52" t="s">
         <v>101</v>
       </c>
-      <c r="H41" s="13">
+      <c r="H52" s="13">
         <v>24000</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>43</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>43</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>46</v>
       </c>
-      <c r="B44">
+      <c r="B55">
         <v>2018</v>
       </c>
-      <c r="C44">
+      <c r="C55">
         <v>2019</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E55" t="s">
         <v>10</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H55" t="s">
         <v>48</v>
       </c>
     </row>

--- a/spark-cv/data/cv_entries.xlsx
+++ b/spark-cv/data/cv_entries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9FE36C-3575-4397-B388-53EDA95DC00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD2DE00-58DE-4E5C-BE0F-465FC3AE433E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="3465" windowWidth="38700" windowHeight="15555" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
+    <workbookView xWindow="51480" yWindow="3300" windowWidth="29040" windowHeight="17790" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="139">
   <si>
     <t>type</t>
   </si>
@@ -445,6 +445,12 @@
   </si>
   <si>
     <t>[Special Issue "Impact of Climate Change on Watershed Hydrology: Latest Advances and Prospects"](https://www.mdpi.com/journal/sustainability/special_issues/19FXHY6N6X), Sustainability</t>
+  </si>
+  <si>
+    <t>ArcAPEX for Agricultural Watershed Modeling Workshop | Uncertainty Analysis (4th Day)</t>
+  </si>
+  <si>
+    <t>April 18-21, 2023</t>
   </si>
 </sst>
 </file>
@@ -523,7 +529,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -535,11 +541,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -547,7 +548,6 @@
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -555,8 +555,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -877,7 +875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D849796-8D2F-2144-8637-FA01837A8DE5}">
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -1016,50 +1014,49 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:12" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="9"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" t="s">
         <v>78</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="7"/>
       <c r="H8" s="1"/>
       <c r="L8" s="5"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -1071,18 +1068,17 @@
       <c r="D9" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" t="s">
         <v>74</v>
       </c>
-      <c r="G9" s="7"/>
       <c r="H9" s="1"/>
       <c r="L9" s="5"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -1094,18 +1090,17 @@
       <c r="D10" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" t="s">
         <v>81</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" t="s">
         <v>82</v>
       </c>
-      <c r="G10" s="7"/>
       <c r="H10" s="1"/>
       <c r="L10" s="5"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -1117,13 +1112,12 @@
       <c r="D11" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="7"/>
       <c r="H11" s="1"/>
       <c r="L11" s="5"/>
     </row>
@@ -1272,145 +1266,143 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D21" s="17"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-    </row>
-    <row r="22" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
+    <row r="21" spans="1:9" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>134</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22">
         <v>2022</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="I22" s="25"/>
-    </row>
-    <row r="23" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="9"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-    </row>
-    <row r="24" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D24" s="9"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-    </row>
-    <row r="25" spans="1:9" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D25" s="23"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-    </row>
-    <row r="26" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="I22" s="19"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="17"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="G26" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" t="s">
         <v>130</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D27" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E27" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F27" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G26" s="15">
+      <c r="G27" s="3">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C28" t="s">
         <v>127</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D28" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E28" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F28" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G27" s="15">
+      <c r="G28" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C29" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D29" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E29" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F29" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G29" s="3">
         <v>39</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C30" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D30" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E30" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F30" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G30" s="3">
         <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="G30" s="15">
-        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1418,19 +1410,19 @@
         <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>93</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G31" s="3">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1438,16 +1430,16 @@
         <v>30</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="G32" s="3">
         <v>20</v>
@@ -1458,62 +1450,62 @@
         <v>30</v>
       </c>
       <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="C34" t="s">
         <v>98</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E34" t="s">
         <v>86</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>88</v>
       </c>
-      <c r="G33">
+      <c r="G34">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D34" s="20"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>102</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" t="s">
-        <v>125</v>
-      </c>
-      <c r="F35" t="s">
-        <v>110</v>
-      </c>
-      <c r="G35">
-        <v>21</v>
-      </c>
+    <row r="35" spans="1:7" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D35" s="16"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>102</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>119</v>
+      <c r="C36" t="s">
+        <v>124</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E36" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F36" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="G36">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1521,19 +1513,19 @@
         <v>102</v>
       </c>
       <c r="C37" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F37" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G37">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1541,38 +1533,50 @@
         <v>102</v>
       </c>
       <c r="C38" t="s">
+        <v>115</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E38" t="s">
+        <v>117</v>
+      </c>
+      <c r="F38" t="s">
+        <v>118</v>
+      </c>
+      <c r="G38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" t="s">
         <v>103</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E38" t="s">
+      <c r="E39" t="s">
         <v>105</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F39" t="s">
         <v>106</v>
       </c>
-      <c r="G38">
+      <c r="G39">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D39" s="3"/>
-    </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="D40" s="3"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>41</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
@@ -1580,7 +1584,7 @@
         <v>41</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1588,7 +1592,7 @@
         <v>41</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1596,7 +1600,7 @@
         <v>41</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1604,7 +1608,7 @@
         <v>41</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1612,7 +1616,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1620,7 +1624,7 @@
         <v>41</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1628,7 +1632,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -1636,24 +1640,15 @@
         <v>41</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>42</v>
-      </c>
-      <c r="C50">
-        <v>2017</v>
+        <v>41</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E50" t="s">
-        <v>73</v>
-      </c>
-      <c r="H50" s="13">
-        <v>5000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -1661,7 +1656,7 @@
         <v>42</v>
       </c>
       <c r="C51">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>99</v>
@@ -1669,7 +1664,7 @@
       <c r="E51" t="s">
         <v>73</v>
       </c>
-      <c r="H51" s="14">
+      <c r="H51" s="10">
         <v>5000</v>
       </c>
     </row>
@@ -1678,24 +1673,33 @@
         <v>42</v>
       </c>
       <c r="C52">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E52" t="s">
-        <v>101</v>
-      </c>
-      <c r="H52" s="13">
-        <v>24000</v>
+        <v>73</v>
+      </c>
+      <c r="H52" s="11">
+        <v>5000</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="C53">
+        <v>2014</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
+      </c>
+      <c r="E53" t="s">
+        <v>101</v>
+      </c>
+      <c r="H53" s="10">
+        <v>24000</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -1703,26 +1707,34 @@
         <v>43</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>43</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>46</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>2018</v>
       </c>
-      <c r="C55">
+      <c r="C56">
         <v>2019</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D56" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E56" t="s">
         <v>10</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H56" t="s">
         <v>48</v>
       </c>
     </row>

--- a/spark-cv/data/cv_entries.xlsx
+++ b/spark-cv/data/cv_entries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD2DE00-58DE-4E5C-BE0F-465FC3AE433E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B020D0B-4261-48A1-BBB8-BE6693910972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="3300" windowWidth="29040" windowHeight="17790" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15555" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="142">
   <si>
     <t>type</t>
   </si>
@@ -451,6 +451,15 @@
   </si>
   <si>
     <t>April 18-21, 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jun. 30, 2023 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uncertainty Quantification of Nitrate Transport Simulation for Integrated Hydrological Models </t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Institute of Agricultural Sciences (NAS) </t>
   </si>
 </sst>
 </file>
@@ -875,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D849796-8D2F-2144-8637-FA01837A8DE5}">
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
@@ -1493,19 +1502,19 @@
         <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="E36" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="F36" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="G36">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1513,19 +1522,19 @@
         <v>102</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E37" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="F37" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="G37">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -1533,19 +1542,19 @@
         <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E38" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F38" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G38">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -1553,38 +1562,50 @@
         <v>102</v>
       </c>
       <c r="C39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" t="s">
+        <v>117</v>
+      </c>
+      <c r="F39" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E40" t="s">
         <v>105</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F40" t="s">
         <v>106</v>
       </c>
-      <c r="G39">
+      <c r="G40">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D40" s="3"/>
-    </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="D41" s="3"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>41</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1592,7 +1613,7 @@
         <v>41</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1600,7 +1621,7 @@
         <v>41</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1608,7 +1629,7 @@
         <v>41</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1616,7 +1637,7 @@
         <v>41</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1624,7 +1645,7 @@
         <v>41</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1632,7 +1653,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -1640,7 +1661,7 @@
         <v>41</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -1648,24 +1669,15 @@
         <v>41</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>42</v>
-      </c>
-      <c r="C51">
-        <v>2017</v>
+        <v>41</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E51" t="s">
-        <v>73</v>
-      </c>
-      <c r="H51" s="10">
-        <v>5000</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -1673,7 +1685,7 @@
         <v>42</v>
       </c>
       <c r="C52">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>99</v>
@@ -1681,7 +1693,7 @@
       <c r="E52" t="s">
         <v>73</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="10">
         <v>5000</v>
       </c>
     </row>
@@ -1690,24 +1702,33 @@
         <v>42</v>
       </c>
       <c r="C53">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E53" t="s">
-        <v>101</v>
-      </c>
-      <c r="H53" s="10">
-        <v>24000</v>
+        <v>73</v>
+      </c>
+      <c r="H53" s="11">
+        <v>5000</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>43</v>
+        <v>42</v>
+      </c>
+      <c r="C54">
+        <v>2014</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>108</v>
+        <v>100</v>
+      </c>
+      <c r="E54" t="s">
+        <v>101</v>
+      </c>
+      <c r="H54" s="10">
+        <v>24000</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -1715,26 +1736,34 @@
         <v>43</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>46</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>2018</v>
       </c>
-      <c r="C56">
+      <c r="C57">
         <v>2019</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D57" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E57" t="s">
         <v>10</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H57" t="s">
         <v>48</v>
       </c>
     </row>

--- a/spark-cv/data/cv_entries.xlsx
+++ b/spark-cv/data/cv_entries.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\spark-brc_gits\spark-brc.github.io\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B020D0B-4261-48A1-BBB8-BE6693910972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8204056-AA5F-4AFE-9C9F-FA39CE5BA2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="38700" windowHeight="15555" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="28800" windowHeight="23550" xr2:uid="{658FACE9-883F-4F49-B936-65547CAA7E51}"/>
   </bookViews>
   <sheets>
     <sheet name="cv_entries" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="147">
   <si>
     <t>type</t>
   </si>
@@ -460,6 +460,21 @@
   </si>
   <si>
     <t xml:space="preserve">National Institute of Agricultural Sciences (NAS) </t>
+  </si>
+  <si>
+    <t>Committee member</t>
+  </si>
+  <si>
+    <t>Fall 2023</t>
+  </si>
+  <si>
+    <t>committee</t>
+  </si>
+  <si>
+    <t>Ali Akram Niazi from Parkistan, Ph.D program in Water Management &amp; Hydrological Science (WMHS), Texas A&amp;M University, Chair: Huilin Gao (WMHS)</t>
+  </si>
+  <si>
+    <t>College Station, Texas, United States</t>
   </si>
 </sst>
 </file>
@@ -538,7 +553,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -569,6 +584,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1281,7 +1299,7 @@
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="63" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>134</v>
       </c>
@@ -1291,16 +1309,29 @@
       <c r="D22" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="20" t="s">
         <v>136</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="I22" s="19"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+    <row r="23" spans="1:9" ht="47.25" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" t="s">
+        <v>143</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
